--- a/client/src/data/raw/mazo_14_alta.xlsx
+++ b/client/src/data/raw/mazo_14_alta.xlsx
@@ -1118,7 +1118,7 @@
         <v>apoyo</v>
       </c>
       <c r="P13" t="str">
-        <v>Programe su cita de seguimiento.</v>
+        <v>cita</v>
       </c>
       <c r="Q13" t="str">
         <v>follow_up</v>
